--- a/artfynd/S 391-2022 artfynd.xlsx
+++ b/artfynd/S 391-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY51"/>
+  <dimension ref="A1:AZ51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -774,6 +779,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/78481538</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -876,6 +886,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/78481510</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -978,6 +993,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/78481511</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1080,6 +1100,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/78481645</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1182,6 +1207,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/78481630</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1289,6 +1319,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/78481515</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1391,6 +1426,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/78481517</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1493,6 +1533,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/78481518</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1595,6 +1640,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/78481602</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1697,6 +1747,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/78481603</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1799,6 +1854,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/78481500</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1905,6 +1965,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/78481502</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2007,6 +2072,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/78481540</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2109,6 +2179,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/78481461</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2211,6 +2286,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/78481463</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2313,6 +2393,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/78481464</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2415,6 +2500,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/78481438</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2517,6 +2607,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/78481563</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2619,6 +2714,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/78481625</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2721,6 +2821,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/78481539</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2823,6 +2928,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/78481595</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2929,6 +3039,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134665307</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3031,6 +3146,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/78481509</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3133,6 +3253,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/78481425</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3235,6 +3360,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/78481629</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3342,6 +3472,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/78481516</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3444,6 +3579,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/78481604</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3546,6 +3686,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/78481606</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3648,6 +3793,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/78481616</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3750,6 +3900,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/78481617</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3852,6 +4007,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/78481619</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3954,6 +4114,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/78481620</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4056,6 +4221,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/78481501</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4158,6 +4328,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/78481559</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4260,6 +4435,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/78481561</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4362,6 +4542,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/78481462</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4464,6 +4649,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/78481475</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4570,6 +4760,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/78481476</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4672,6 +4867,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/78481477</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4774,6 +4974,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/78481444</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -4876,6 +5081,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/78481445</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -4978,6 +5188,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/78481446</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5080,6 +5295,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/78481564</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5186,6 +5406,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134665308</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5292,6 +5517,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129001276</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5403,6 +5633,11 @@
           <t>C250246 Ljusdal NVI 2025</t>
         </is>
       </c>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132325675</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5513,6 +5748,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125221118</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5619,6 +5859,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126017021</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5725,6 +5970,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124326754</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -5850,8 +6100,65 @@
           <t>WWF - Tillsammans för Sveriges igelkottar</t>
         </is>
       </c>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127852080</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/S 391-2022 artfynd.xlsx
+++ b/artfynd/S 391-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ51"/>
+  <dimension ref="A1:AZ52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5525,48 +5525,48 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>132325675</v>
+        <v>136005636</v>
       </c>
       <c r="B47" t="n">
-        <v>111153</v>
+        <v>80556</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>220240</v>
+        <v>6458</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Linnea</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Linnaea borealis</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Hennan, Hls</t>
+          <t>Abborrtjärnen, Abborrtjärnen, Hls</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>535859</v>
+        <v>527293</v>
       </c>
       <c r="R47" t="n">
-        <v>6874961</v>
+        <v>6878453</v>
       </c>
       <c r="S47" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5590,22 +5590,22 @@
       </c>
       <c r="Y47" t="inlineStr">
         <is>
-          <t>2025-06-26</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>15:12</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2025-06-26</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>15:12</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5620,76 +5620,65 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Milad Avalinejad Bandari</t>
+          <t>David Isaksson</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Milad Avalinejad Bandari, Alexander Schäpers</t>
-        </is>
-      </c>
-      <c r="AY47" t="inlineStr">
-        <is>
-          <t>C250246 Ljusdal NVI 2025</t>
-        </is>
-      </c>
+          <t>David Isaksson, Elin Lönnberg</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr"/>
       <c r="AZ47" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132325675</t>
+          <t>https://artportalen.se/Sighting/136005636</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>125221118</v>
+        <v>132325675</v>
       </c>
       <c r="B48" t="n">
-        <v>79084</v>
+        <v>111153</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6446</v>
+        <v>220240</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Linnea</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Linnaea borealis</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J48" t="inlineStr"/>
-      <c r="K48" t="inlineStr"/>
-      <c r="N48" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Skålvallen, Hls</t>
+          <t>Hennan, Hls</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>533812</v>
+        <v>535859</v>
       </c>
       <c r="R48" t="n">
-        <v>6874415</v>
+        <v>6874961</v>
       </c>
       <c r="S48" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5713,17 +5702,22 @@
       </c>
       <c r="Y48" t="inlineStr">
         <is>
-          <t>2025-05-14</t>
+          <t>2025-06-26</t>
+        </is>
+      </c>
+      <c r="Z48" t="inlineStr">
+        <is>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2025-05-14</t>
-        </is>
-      </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+          <t>2025-06-26</t>
+        </is>
+      </c>
+      <c r="AB48" t="inlineStr">
+        <is>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5732,34 +5726,37 @@
       <c r="AE48" t="b">
         <v>0</v>
       </c>
-      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
       </c>
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Milad Avalinejad Bandari</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AY48" t="inlineStr"/>
+          <t>Milad Avalinejad Bandari, Alexander Schäpers</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr">
+        <is>
+          <t>C250246 Ljusdal NVI 2025</t>
+        </is>
+      </c>
       <c r="AZ48" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/125221118</t>
+          <t>https://artportalen.se/Sighting/132325675</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>126017021</v>
+        <v>125221118</v>
       </c>
       <c r="B49" t="n">
-        <v>79085</v>
+        <v>79084</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5767,21 +5764,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -5789,19 +5786,22 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J49" t="inlineStr"/>
+      <c r="K49" t="inlineStr"/>
+      <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
           <t>Skålvallen, Hls</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>534970</v>
+        <v>533812</v>
       </c>
       <c r="R49" t="n">
-        <v>6870688</v>
+        <v>6874415</v>
       </c>
       <c r="S49" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5825,12 +5825,12 @@
       </c>
       <c r="Y49" t="inlineStr">
         <is>
-          <t>2025-06-03</t>
+          <t>2025-05-14</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2025-06-03</t>
+          <t>2025-05-14</t>
         </is>
       </c>
       <c r="AC49" t="inlineStr">
@@ -5844,6 +5844,7 @@
       <c r="AE49" t="b">
         <v>0</v>
       </c>
+      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
       </c>
@@ -5861,16 +5862,16 @@
       <c r="AY49" t="inlineStr"/>
       <c r="AZ49" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126017021</t>
+          <t>https://artportalen.se/Sighting/125221118</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>124326754</v>
+        <v>126017021</v>
       </c>
       <c r="B50" t="n">
-        <v>79084</v>
+        <v>79085</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5878,21 +5879,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
@@ -5902,17 +5903,17 @@
       </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Backarvall, Hls</t>
+          <t>Skålvallen, Hls</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>539355</v>
+        <v>534970</v>
       </c>
       <c r="R50" t="n">
-        <v>6867103</v>
+        <v>6870688</v>
       </c>
       <c r="S50" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -5936,17 +5937,17 @@
       </c>
       <c r="Y50" t="inlineStr">
         <is>
-          <t>2025-04-09</t>
+          <t>2025-06-03</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>2025-04-09</t>
+          <t>2025-06-03</t>
         </is>
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>Påträffad under Sveaskogs naturvärdesinventering.</t>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5972,38 +5973,38 @@
       <c r="AY50" t="inlineStr"/>
       <c r="AZ50" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124326754</t>
+          <t>https://artportalen.se/Sighting/126017021</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>127852080</v>
+        <v>124326754</v>
       </c>
       <c r="B51" t="n">
-        <v>56845</v>
+        <v>79084</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100053</v>
+        <v>6446</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Igelkott</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Erinaceus europaeus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
@@ -6011,29 +6012,19 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K51" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="N51" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Ljusdals kommun, Hls</t>
+          <t>Backarvall, Hls</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>536489</v>
+        <v>539355</v>
       </c>
       <c r="R51" t="n">
-        <v>6866145</v>
+        <v>6867103</v>
       </c>
       <c r="S51" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6052,27 +6043,22 @@
       </c>
       <c r="W51" t="inlineStr">
         <is>
-          <t>Färila</t>
+          <t>Ljusdal</t>
         </is>
       </c>
       <c r="Y51" t="inlineStr">
         <is>
-          <t>2025-08-19</t>
-        </is>
-      </c>
-      <c r="Z51" t="inlineStr">
-        <is>
-          <t>06:21</t>
+          <t>2025-04-09</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2025-08-19</t>
-        </is>
-      </c>
-      <c r="AB51" t="inlineStr">
-        <is>
-          <t>06:21</t>
+          <t>2025-04-09</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering.</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6087,20 +6073,146 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX51" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124326754</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>127852080</v>
+      </c>
+      <c r="B52" t="n">
+        <v>56845</v>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>100053</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Igelkott</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Erinaceus europaeus</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>Ljusdals kommun, Hls</t>
+        </is>
+      </c>
+      <c r="Q52" t="n">
+        <v>536489</v>
+      </c>
+      <c r="R52" t="n">
+        <v>6866145</v>
+      </c>
+      <c r="S52" t="n">
+        <v>1</v>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>Färila</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>2025-08-19</t>
+        </is>
+      </c>
+      <c r="Z52" t="inlineStr">
+        <is>
+          <t>06:21</t>
+        </is>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>2025-08-19</t>
+        </is>
+      </c>
+      <c r="AB52" t="inlineStr">
+        <is>
+          <t>06:21</t>
+        </is>
+      </c>
+      <c r="AD52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT52" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
           <t>Johan Möller</t>
         </is>
       </c>
-      <c r="AX51" t="inlineStr">
+      <c r="AX52" t="inlineStr">
         <is>
           <t>Via Johan Möller</t>
         </is>
       </c>
-      <c r="AY51" t="inlineStr">
+      <c r="AY52" t="inlineStr">
         <is>
           <t>WWF - Tillsammans för Sveriges igelkottar</t>
         </is>
       </c>
-      <c r="AZ51" t="inlineStr">
+      <c r="AZ52" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/127852080</t>
         </is>
@@ -6158,6 +6270,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
